--- a/100.xlsx
+++ b/100.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4293,7 +4293,58 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="P74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>444</v>
+      </c>
+      <c r="D75" t="n">
+        <v>408</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>444</v>
+      </c>
+      <c r="L75" t="n">
+        <v>408</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/100.xlsx
+++ b/100.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4344,7 +4344,58 @@
       <c r="O75" t="n">
         <v>0.26</v>
       </c>
-      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>795</v>
+      </c>
+      <c r="D76" t="n">
+        <v>651</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>795</v>
+      </c>
+      <c r="L76" t="n">
+        <v>651</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/100.xlsx
+++ b/100.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4395,7 +4395,160 @@
       <c r="O76" t="n">
         <v>7.03</v>
       </c>
-      <c r="P76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1124</v>
+      </c>
+      <c r="D77" t="n">
+        <v>608</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1124</v>
+      </c>
+      <c r="L77" t="n">
+        <v>608</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2160</v>
+      </c>
+      <c r="D78" t="n">
+        <v>176</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2160</v>
+      </c>
+      <c r="L78" t="n">
+        <v>176</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1249</v>
+      </c>
+      <c r="D79" t="n">
+        <v>161</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1249</v>
+      </c>
+      <c r="L79" t="n">
+        <v>161</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/100.xlsx
+++ b/100.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4548,7 +4548,58 @@
       <c r="O79" t="n">
         <v>1.26</v>
       </c>
-      <c r="P79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2642</v>
+      </c>
+      <c r="D80" t="n">
+        <v>6309</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2642</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6309</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
